--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92562080057</v>
+        <v>46157.93071075482</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93071075482</v>
+        <v>46157.93153792941</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93153792941</v>
+        <v>46157.93393780688</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93393780688</v>
+        <v>46157.93708509533</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93708509533</v>
+        <v>46158.282107769</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.282107769</v>
+        <v>46158.29665893054</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29665893054</v>
+        <v>46158.29805492156</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29805492156</v>
+        <v>46158.33381527165</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33381527165</v>
+        <v>46158.3684827947</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Май/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3684827947</v>
+        <v>46158.37281720019</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
